--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac-020/Desktop/jjjshop-saas/jjj_food_chain/public/imports/product/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEBF594-CEEE-F246-928D-AFEE4583F650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9900" yWindow="5180" windowWidth="40140" windowHeight="14680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="21020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>*Ürün Adı</t>
   </si>
@@ -30,7 +37,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Kategori
@@ -41,7 +48,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>(Lütfen ikincil sınıflandırmaları / ile ayırın)</t>
@@ -53,7 +60,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Stok Hesaplama Yöntemi
@@ -64,7 +71,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>(Sipariş Verme İle Stok Azaltma=1/Ödeme İle Stok Azaltma=2)</t>
@@ -85,7 +92,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Stok miktarı
@@ -96,7 +103,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>(Maksimum envanter: 999999999)</t>
@@ -114,7 +121,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Ürün durumu
@@ -125,7 +132,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>(Raflara koy=1/Raflardan kaldırıldı=0)</t>
@@ -139,13 +146,75 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Fiyatlandırma Yöntemi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Tam sayı olarak fiyatlandırılır=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Ondalık olarak fiyatlandırılır=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">*Göster
 </t>
     </r>
@@ -154,10 +223,11 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/QR kod ile sipariş=5)</t>
+      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/QR kod ile sipariş=5)
+(Dikkat: Fiyatlandırma yöntemi=2 olduğunda, yalnızca şu cihazlarda görüntülenebilir: Kasa 1/Mutfak Ekranı 3)</t>
     </r>
   </si>
   <si>
@@ -165,6 +235,29 @@
   </si>
   <si>
     <t>Satın alma sınırı</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Üye İndirimi
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Aç=1/Kapat=0)</t>
+    </r>
   </si>
   <si>
     <t>(Örnek, içe aktarırken bu satırı silin)
@@ -186,79 +279,403 @@
   <si>
     <t>likör</t>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Üye İndirimi
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Aç=1/Kapat=0)</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -266,9 +683,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -285,21 +944,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -509,34 +1212,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="27.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.13970588235294" style="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="1"/>
-    <col min="13" max="13" width="62" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="9.13970588235294" style="1"/>
+    <col min="13" max="13" width="28.8014705882353" style="1" customWidth="1"/>
+    <col min="14" max="14" width="62" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="80" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,31 +1280,34 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>19</v>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+    <row r="2" ht="159" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -612,26 +1319,26 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="1">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1">
         <v>12345</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
       </c>
       <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1"/>
+    <row r="4" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
@@ -639,8 +1346,8 @@
       <c r="K4" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21020"/>
+    <workbookView windowHeight="21780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -226,7 +232,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/QR kod ile sipariş=5)
+      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/QR kod ile sipariş=5/Paket Servis=6)
 (Dikkat: Fiyatlandırma yöntemi=2 olduğunda, yalnızca şu cihazlarda görüntülenebilir: Kasa 1/Mutfak Ekranı 3)</t>
     </r>
   </si>
@@ -1325,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="N2" s="1">
-        <v>12345</v>
+        <v>123456</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>

--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>*Ürün Adı</t>
   </si>
@@ -221,6 +221,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">*Göster
 </t>
     </r>
@@ -252,6 +259,22 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Üye İndirimi
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Aç=1/Kapat=0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tüm Sipariş İndirimi
 </t>
     </r>
     <r>
@@ -1224,7 +1247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
@@ -1243,10 +1266,11 @@
     <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
     <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.13970588235294" style="1"/>
+    <col min="18" max="18" width="18.6323529411765" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="80" customHeight="1" spans="1:17">
+    <row r="1" ht="80" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1298,22 +1322,25 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="159" spans="1:17">
+    <row r="2" ht="159" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -1325,10 +1352,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" s="1">
         <v>123456</v>
@@ -1340,6 +1367,9 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
         <v>1</v>
       </c>
     </row>

--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21780"/>
+    <workbookView windowWidth="3264" windowHeight="21940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -274,6 +274,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Tüm Sipariş İndirimi
 </t>
     </r>
@@ -289,15 +296,216 @@
     </r>
   </si>
   <si>
-    <t>(Örnek, içe aktarırken bu satırı silin)
+    <r>
+      <t xml:space="preserve">(Örnek, içe aktarırken bu satırı silin)
 English:Caramel pudding
-ภาษาไทย:พุดดิ้งคาราเมล
-简体中文:焦糖布丁
-繁體中文:焦糖布丁
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-日本語:クレームブリュレ
-한국어:크림 브륄레</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+Svenska:Karamellpudding</t>
+    </r>
   </si>
   <si>
     <t>Tatlılar/Hong Kong Usulü Tatlılar</t>
@@ -319,7 +527,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -507,6 +715,24 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Apple SD Gothic Neo"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1326,7 +1552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="159" spans="1:18">
+    <row r="2" ht="176" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>

--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="3264" windowHeight="21940"/>
+    <workbookView windowHeight="23860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>*Ürün Adı</t>
   </si>
@@ -40,7 +40,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">*Kategori
+      <t xml:space="preserve">*Sınıflandırma
 </t>
     </r>
     <r>
@@ -55,94 +55,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*Stok Hesaplama Yöntemi
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Sipariş Verme İle Stok Azaltma=1/Ödeme İle Stok Azaltma=2)</t>
-    </r>
-  </si>
-  <si>
-    <t>*Ürün Birimi</t>
-  </si>
-  <si>
-    <t>*Spesifikasyon adı</t>
-  </si>
-  <si>
-    <t>Resim Adı</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*Stok miktarı
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Maksimum envanter: 999999999)</t>
-    </r>
-  </si>
-  <si>
-    <t>Ürün barkodu</t>
-  </si>
-  <si>
-    <t>*Ürün fiyatı</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*Ürün durumu
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Raflara koy=1/Raflardan kaldırıldı=0)</t>
-    </r>
-  </si>
-  <si>
-    <t>*Yerinde yemek vergisi</t>
-  </si>
-  <si>
-    <t>*Paket servis vergisi</t>
+    <t>*Birim</t>
+  </si>
+  <si>
+    <t>*Spesifikasy</t>
+  </si>
+  <si>
+    <t>*Fiyat</t>
   </si>
   <si>
     <r>
@@ -152,35 +71,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Fiyatlandırma Yöntemi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+      <t xml:space="preserve">*Fiyatlandırma yöntemi
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
     </r>
     <r>
       <rPr>
@@ -189,16 +81,22 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Tam sayı olarak fiyatlandırılır=1</t>
+      <t>(Tamsayı fiyatlandırma = 1 / Ondalık fiyatlandırma = 2)</t>
     </r>
+  </si>
+  <si>
+    <t>Barkod</t>
+  </si>
+  <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <rFont val="宋体-简"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>，</t>
+      <t xml:space="preserve">*Raflara yerleştirme
+</t>
     </r>
     <r>
       <rPr>
@@ -207,56 +105,47 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Ondalık olarak fiyatlandırılır=2</t>
+      <t>(Açık = 0 / Kapalı = 1)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+  </si>
+  <si>
+    <t>*Yerinde yemek vergisi</t>
+  </si>
+  <si>
+    <t>*Paket servis vergisi</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">*Göster
+      <t xml:space="preserve">*Stok azalması
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/QR kod ile sipariş=5/Paket Servis=6)
-(Dikkat: Fiyatlandırma yöntemi=2 olduğunda, yalnızca şu cihazlarda görüntülenebilir: Kasa 1/Mutfak Ekranı 3)</t>
+      <t>(Sipariş azalması = 1/ödeme azalması = 2)</t>
     </r>
   </si>
   <si>
-    <t>Ürün sıralaması</t>
-  </si>
-  <si>
-    <t>Satın alma sınırı</t>
+    <t>*Göster
+(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/Masa kodu sipariş=5/QR kod ile sipariş=6)</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Üye İndirimi
 </t>
@@ -265,51 +154,13 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Aç=1/Kapat=0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tüm Sipariş İndirimi
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Aç=1/Kapat=0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">(Örnek, içe aktarırken bu satırı silin)
-English:Caramel pudding
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>ภาษาไทย</t>
+      <t>(Aç=0/Kapat=1)</t>
     </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -317,204 +168,42 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>:</t>
+      <t xml:space="preserve">Toplam sipariş indirimi
+</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>พุดดิ้งคาราเมล</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>(Açık=0/Kapalı=1)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>简体中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>繁體中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+  </si>
+  <si>
+    <t>(Örnek, içe aktarırken bu satırı silin)
+English:Caramel pudding
+ภาษาไทย:พุดดิ้งคาราเมล
+简体中文:焦糖布丁
+繁體中文:焦糖布丁
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日本語</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="冬青黑体简体中文"/>
-        <charset val="134"/>
-      </rPr>
-      <t>クレームブリュレ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>크림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>브륄레</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+日本語:クレームブリュレ
+한국어:크림 브륄레
 Svenska:Karamellpudding</t>
-    </r>
   </si>
   <si>
     <t>Tatlılar/Hong Kong Usulü Tatlılar</t>
   </si>
   <si>
-    <t>hediyeler için sınıflandırıcı</t>
-  </si>
-  <si>
-    <t>likör</t>
+    <t>bir</t>
+  </si>
+  <si>
+    <t>Standart</t>
+  </si>
+  <si>
+    <t>Alkollü içecekler</t>
   </si>
 </sst>
 </file>
@@ -527,7 +216,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -695,45 +384,22 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体-简"/>
+      <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体-简"/>
+      <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="冬青黑体简体中文"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Apple SD Gothic Neo"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1186,20 +852,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1473,139 +1136,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5735294117647" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.13970588235294" style="1"/>
-    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.13970588235294" style="1"/>
-    <col min="13" max="13" width="28.8014705882353" style="1" customWidth="1"/>
-    <col min="14" max="14" width="62" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12" style="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6323529411765" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.13970588235294" style="1"/>
+    <col min="6" max="6" width="46.7132352941176" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7132352941176" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5735294117647" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7132352941176" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5735294117647" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.7132352941176" style="1" customWidth="1"/>
+    <col min="12" max="12" width="121.573529411765" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.2867647058824" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="80" customHeight="1" spans="1:18">
+    <row r="1" ht="61" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" ht="176" spans="1:14">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="176" spans="1:18">
-      <c r="A2" s="2" t="s">
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I2" s="1">
-        <v>50</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="L2" s="1">
+        <v>1234567</v>
+      </c>
+      <c r="M2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N2" s="1">
-        <v>123456</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
         <v>1</v>
       </c>
-      <c r="R2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1"/>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="K4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>

--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -216,7 +216,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -386,13 +386,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1236,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>1234567</v>
+        <v>123456</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>

--- a/admin/public/imports/product/tr.xlsx
+++ b/admin/public/imports/product/tr.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>*Ürün Adı</t>
   </si>
@@ -40,7 +40,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">*Sınıflandırma
+      <t xml:space="preserve">*Kategori
 </t>
     </r>
     <r>
@@ -55,13 +55,94 @@
     </r>
   </si>
   <si>
-    <t>*Birim</t>
-  </si>
-  <si>
-    <t>*Spesifikasy</t>
-  </si>
-  <si>
-    <t>*Fiyat</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Stok Hesaplama Yöntemi
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Sipariş Verme İle Stok Azaltma=1/Ödeme İle Stok Azaltma=2)</t>
+    </r>
+  </si>
+  <si>
+    <t>*Ürün Birimi</t>
+  </si>
+  <si>
+    <t>*Spesifikasyon adı</t>
+  </si>
+  <si>
+    <t>Resim Adı</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Stok miktarı
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Maksimum envanter: 999999999)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ürün barkodu</t>
+  </si>
+  <si>
+    <t>*Ürün fiyatı</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Ürün durumu
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Raflara koy=1/Raflardan kaldırıldı=0)</t>
+    </r>
+  </si>
+  <si>
+    <t>*Yerinde yemek vergisi</t>
+  </si>
+  <si>
+    <t>*Paket servis vergisi</t>
   </si>
   <si>
     <r>
@@ -71,81 +152,104 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">*Fiyatlandırma yöntemi
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Fiyatlandırma Yöntemi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>(Tamsayı fiyatlandırma = 1 / Ondalık fiyatlandırma = 2)</t>
-    </r>
-  </si>
-  <si>
-    <t>Barkod</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t>Tam sayı olarak fiyatlandırılır=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">*Raflara yerleştirme
+      <t>Ondalık olarak fiyatlandırılır=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*Göster
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(Açık = 0 / Kapalı = 1)</t>
-    </r>
-  </si>
-  <si>
-    <t>*Yerinde yemek vergisi</t>
-  </si>
-  <si>
-    <t>*Paket servis vergisi</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">*Stok azalması
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(Sipariş azalması = 1/ödeme azalması = 2)</t>
-    </r>
-  </si>
-  <si>
-    <t>*Göster
-(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/Masa kodu sipariş=5/QR kod ile sipariş=6)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Çoktan seçmeli, görüntülenip görüntülenmeyeceği: Kasa=1/Tablet=2/Mutfak Ekranı=3/Sipariş asistanı=4/Masa kodu sipariş=5/QR kod ile sipariş=6)
+(Dikkat: Fiyatlandırma yöntemi=2 olduğunda, yalnızca şu cihazlarda görüntülenebilir: Kasa 1/Mutfak Ekranı 3)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ürün sıralaması</t>
+  </si>
+  <si>
+    <t>Satın alma sınırı</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Üye İndirimi
 </t>
@@ -154,13 +258,57 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Aç=1/Kapat=0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tüm Sipariş İndirimi
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Aç=1/Kapat=0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>(Aç=0/Kapat=1)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">(Örnek, içe aktarırken bu satırı silin)
+English:Caramel pudding
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -168,42 +316,204 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">Toplam sipariş indirimi
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>(Açık=0/Kapalı=1)</t>
-    </r>
-  </si>
-  <si>
-    <t>(Örnek, içe aktarırken bu satırı silin)
-English:Caramel pudding
-ภาษาไทย:พุดดิ้งคาราเมล
-简体中文:焦糖布丁
-繁體中文:焦糖布丁
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-日本語:クレームブリュレ
-한국어:크림 브륄레
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Svenska:Karamellpudding</t>
+    </r>
   </si>
   <si>
     <t>Tatlılar/Hong Kong Usulü Tatlılar</t>
   </si>
   <si>
-    <t>bir</t>
-  </si>
-  <si>
-    <t>Standart</t>
-  </si>
-  <si>
-    <t>Alkollü içecekler</t>
+    <t>hediyeler için sınıflandırıcı</t>
+  </si>
+  <si>
+    <t>likör</t>
   </si>
 </sst>
 </file>
@@ -216,7 +526,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -384,15 +694,45 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Apple SD Gothic Neo"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -845,17 +1185,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1129,114 +1472,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="1"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5735294117647" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.7132352941176" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7132352941176" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5735294117647" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7132352941176" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5735294117647" style="1" customWidth="1"/>
-    <col min="11" max="11" width="32.7132352941176" style="1" customWidth="1"/>
-    <col min="12" max="12" width="121.573529411765" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.2867647058824" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5735294117647" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.13970588235294" style="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.13970588235294" style="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.13970588235294" style="1"/>
+    <col min="13" max="13" width="28.8014705882353" style="1" customWidth="1"/>
+    <col min="14" max="14" width="62" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6323529411765" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="61" customHeight="1" spans="1:16">
+    <row r="1" ht="80" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="176" spans="1:14">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
+    <row r="2" ht="176" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="3">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I2" s="1">
         <v>50</v>
       </c>
-      <c r="F2" s="1">
+      <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1">
+        <v>123456</v>
+      </c>
+      <c r="O2" s="1">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="1">
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
-      <c r="L2" s="1">
-        <v>123456</v>
-      </c>
-      <c r="M2" s="1">
+      <c r="R2" s="1">
         <v>1</v>
       </c>
-      <c r="N2" s="1">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1"/>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="K4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
